--- a/web/files/港岛-北角-嘉居．天后.xlsx
+++ b/web/files/港岛-北角-嘉居．天后.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -896,7 +896,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5474,7 +5474,7 @@
           <t>A | 857呎 (3房)
 $2980万
 $34,772/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -5491,7 +5491,7 @@
           <t>A | 477呎 (3房)
 $1368万
 $28,679/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -5499,7 +5499,7 @@
           <t>B | 361呎 (2房)
 $1068万
 $29,584/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -5507,7 +5507,7 @@
           <t>C | 361呎 (2房)
 $1168万
 $32,355/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
           <t>A | 477呎 (3房)
 $1339万
 $28,067/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -5530,7 +5530,7 @@
           <t>B | 361呎 (2房)
 $1048万
 $29,030/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -5538,7 +5538,7 @@
           <t>C | 361呎 (2房)
 $1148万
 $31,801/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
           <t>A | 477呎 (3房)
 $1312万
 $27,497/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -5561,7 +5561,7 @@
           <t>B | 361呎 (2房)
 $1021万
 $28,277/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -5569,7 +5569,7 @@
           <t>C | 361呎 (2房)
 $1165万
 $32,269/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
     </row>
@@ -5584,7 +5584,7 @@
           <t>A | 477呎 (3房)
 $1301万
 $27,279/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -5592,7 +5592,7 @@
           <t>B | 361呎 (2房)
 $1013万
 $28,050/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -5600,7 +5600,7 @@
           <t>C | 361呎 (2房)
 $1102万
 $30,521/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5615,7 @@
           <t>A | 477呎 (3房)
 $1348万
 $28,252/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -5623,7 +5623,7 @@
           <t>B | 361呎 (2房)
 $1012万
 $28,028/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -5631,7 +5631,7 @@
           <t>C | 361呎 (2房)
 $1088万
 $30,139/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
           <t>A | 477呎 (3房)
 $1327万
 $27,822/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -5654,7 +5654,7 @@
           <t>B | 361呎 (2房)
 $997万
 $27,607/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -5662,7 +5662,7 @@
           <t>C | 361呎 (2房)
 $1063万
 $29,446/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
     </row>
@@ -5677,7 +5677,7 @@
           <t>A | 477呎 (3房)
 $1270万
 $26,623/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -5685,7 +5685,7 @@
           <t>B | 361呎 (2房)
 $989万
 $27,391/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -5693,7 +5693,7 @@
           <t>C | 361呎 (2房)
 $1051万
 $29,108/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
           <t>A | 477呎 (3房)
 $1260万
 $26,419/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -5716,7 +5716,7 @@
           <t>B | 361呎 (2房)
 $981万
 $27,169/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -5724,7 +5724,7 @@
           <t>C | 361呎 (2房)
 $1038万
 $28,753/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
           <t>A | 477呎 (3房)
 $1250万
 $26,212/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -5747,7 +5747,7 @@
           <t>B | 361呎 (2房)
 $973万
 $26,961/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -5755,7 +5755,7 @@
           <t>C | 361呎 (2房)
 $1026万
 $28,421/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
           <t>A | 477呎 (3房)
 $1238万
 $25,950/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -5778,7 +5778,7 @@
           <t>B | 361呎 (2房)
 $966万
 $26,745/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -5786,7 +5786,7 @@
           <t>C | 361呎 (2房)
 $1016万
 $28,133/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
           <t>A | 477呎 (3房)
 $1228万
 $25,748/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -5809,7 +5809,7 @@
           <t>B | 361呎 (2房)
 $958万
 $26,532/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -5817,7 +5817,7 @@
           <t>C | 361呎 (2房)
 $1006万
 $27,853/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
           <t>A | 477呎 (3房)
 $1218万
 $25,541/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -5840,7 +5840,7 @@
           <t>B | 361呎 (2房)
 $950万
 $26,321/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -5848,7 +5848,7 @@
           <t>C | 361呎 (2房)
 $996万
 $27,576/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
           <t>A | 477呎 (3房)
 $1209万
 $25,342/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -5871,7 +5871,7 @@
           <t>B | 361呎 (2房)
 $943万
 $26,111/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -5879,7 +5879,7 @@
           <t>C | 361呎 (2房)
 $986万
 $27,302/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
           <t>A | 477呎 (3房)
 $1199万
 $25,143/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -5902,7 +5902,7 @@
           <t>B | 361呎 (2房)
 $935万
 $25,900/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -5910,7 +5910,7 @@
           <t>C | 361呎 (2房)
 $976万
 $27,036/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -5925,7 +5925,7 @@
           <t>A | 477呎 (3房)
 $1190万
 $24,939/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -5933,7 +5933,7 @@
           <t>B | 361呎 (2房)
 $928万
 $25,701/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -5941,7 +5941,7 @@
           <t>C | 361呎 (2房)
 $966万
 $26,767/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
           <t>A | 477呎 (3房)
 $1180万
 $24,742/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -5964,7 +5964,7 @@
           <t>B | 361呎 (2房)
 $920万
 $25,493/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -5972,7 +5972,7 @@
           <t>C | 361呎 (2房)
 $947万
 $26,241/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5987,7 @@
           <t>A | 477呎 (3房)
 $1170万
 $24,526/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -5995,7 +5995,7 @@
           <t>B | 361呎 (2房)
 $913万
 $25,291/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -6003,7 +6003,7 @@
           <t>C | 361呎 (2房)
 $940万
 $26,033/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
           <t>A | 477呎 (3房)
 $1162万
 $24,356/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -6026,7 +6026,7 @@
           <t>B | 361呎 (2房)
 $906万
 $25,091/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -6034,7 +6034,7 @@
           <t>C | 361呎 (2房)
 $932万
 $25,823/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6049,7 @@
           <t>A | 477呎 (3房)
 $1150万
 $24,109/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -6057,7 +6057,7 @@
           <t>B | 361呎 (2房)
 $899万
 $24,898/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -6065,7 +6065,7 @@
           <t>C | 361呎 (2房)
 $925万
 $25,623/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6080,7 @@
           <t>A | 477呎 (3房)
 $1140万
 $23,895/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -6088,7 +6088,7 @@
           <t>B | 361呎 (2房)
 $892万
 $24,695/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -6096,7 +6096,7 @@
           <t>C | 361呎 (2房)
 $918万
 $25,418/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
           <t>A | 477呎 (3房)
 $1132万
 $23,727/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -6119,7 +6119,7 @@
           <t>B | 361呎 (2房)
 $916万
 $25,388/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -6127,7 +6127,7 @@
           <t>C | 361呎 (2房)
 $944万
 $26,139/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6142,7 @@
           <t>A | 477呎 (3房)
 $1123万
 $23,539/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -6150,7 +6150,7 @@
           <t>B | 361呎 (2房)
 $878万
 $24,307/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -6158,7 +6158,7 @@
           <t>C | 361呎 (2房)
 $903万
 $25,019/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
           <t>A | 477呎 (3房)
 $1154万
 $24,203/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -6181,7 +6181,7 @@
           <t>B | 361呎 (2房)
 $870万
 $24,108/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -6189,7 +6189,7 @@
           <t>C | 361呎 (2房)
 $896万
 $24,809/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
           <t>A | 439呎 (3房)
 $1449万
 $33,002/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -6212,7 +6212,7 @@
           <t>B | 324呎 (2房)
 $1080万
 $33,333/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -6220,7 +6220,7 @@
           <t>C | 324呎 (2房)
 $1098万
 $33,889/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-北角-嘉居．天后.xlsx
+++ b/web/files/港岛-北角-嘉居．天后.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -5474,7 +5474,7 @@
           <t>A | 857呎 (3房)
 $2980万
 $34,772/呎
-(26年-07月-22日)</t>
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
